--- a/JsonConverter/ExcelFiles/OO_Character.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Character.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\ComputerBasics_DaniTech_Work\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
   </bookViews>
@@ -17,14 +12,14 @@
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -47,42 +42,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>character_hellena_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>헬레나</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 마법을 사용할 수 있는 캐릭터</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_victor_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>빅토르</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>소환 마법을 사용할 수 있는 캐릭터</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_daniel_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>다니엘</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>잉여로운 버프 캐릭터</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>스킬</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -95,18 +54,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>skill_rest_coffee_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_fireball_01,skill_normalSword_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_normalSword_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>캐릭터 별로 무기가 고정인 경우용</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -115,30 +62,26 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_Sword_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon_CoffeeCup_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon_Braclet_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>BasicCostumeId</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Costume_03</t>
+    <t>나레이션</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_narrator_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>프롤로그와 에필로그를 진행하는 서술자</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="9">
     <font>
       <sz val="10"/>
@@ -557,10 +500,10 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="13">
@@ -574,13 +517,13 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="13" customFormat="1" ht="15.75" customHeight="1">
@@ -594,34 +537,28 @@
         <v>6</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>28</v>
-      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="16"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -633,21 +570,11 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -660,21 +587,11 @@
       <c r="O5" s="5"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>

--- a/JsonConverter/ExcelFiles/OO_Character.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Character.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -70,11 +70,35 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>프롤로그와 에필로그를 진행하는 서술자</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>character_narrator_01</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>프롤로그와 에필로그를 진행하는 서술자</t>
+    <t>character_Moran_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_JangYoungSim_03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>모란</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">장영심 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 게임의 주인공</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 게임의 주인공의 아버지</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -548,13 +572,13 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -570,9 +594,15 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -587,9 +617,15 @@
       <c r="O5" s="5"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
+      <c r="A6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>

--- a/JsonConverter/ExcelFiles/OO_Character.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Character.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -78,27 +78,51 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>모란</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">장영심 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 게임의 주인공</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 게임의 주인공의 아버지</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_JangYoungSim_03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>주인공의 첫번째 동료</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_04</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>재익군</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_05</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>춘양</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>주인공의 두번째 동료이자 재익의 주인</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>character_Moran_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_JangYoungSim_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>모란</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">장영심 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 게임의 주인공</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 게임의 주인공의 아버지</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -595,13 +619,13 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -618,13 +642,13 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -640,9 +664,15 @@
       <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -657,9 +687,15 @@
       <c r="O7" s="5"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
+      <c r="A8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>

--- a/JsonConverter/ExcelFiles/OO_Character.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Character.xlsx
@@ -1,201 +1,90 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Character" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
-  <si>
-    <t>캐릭터 고유 ID</t>
-  </si>
-  <si>
-    <t>캐릭터 전체 컨셉이나 스토리</t>
-  </si>
-  <si>
-    <t>(name)</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>스킬</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillList</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐릭터 별로 무기가 고정인 경우용</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>UseWeaponId</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicCostumeId</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>나레이션</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>프롤로그와 에필로그를 진행하는 서술자</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_narrator_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>모란</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">장영심 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 게임의 주인공</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 게임의 주인공의 아버지</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_JangYoungSim_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>주인공의 첫번째 동료</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Mr.Jaeik_04</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>재익군</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Chunyang_05</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>춘양</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>주인공의 두번째 동료이자 재익의 주인</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Moran_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="10">
     <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF008000"/>
       <sz val="11"/>
-      <color rgb="FF008000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -226,14 +115,29 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -279,50 +183,121 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -523,430 +498,502 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="50.7265625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.26953125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="12.54296875" style="3"/>
+    <col width="15" customWidth="1" style="3" min="1" max="1"/>
+    <col width="14" customWidth="1" style="3" min="2" max="2"/>
+    <col width="14" customWidth="1" style="3" min="3" max="3"/>
+    <col width="14" customWidth="1" style="3" min="4" max="4"/>
+    <col width="14" customWidth="1" style="3" min="5" max="5"/>
+    <col width="14" customWidth="1" style="3" min="6" max="6"/>
+    <col width="12.54296875" customWidth="1" style="3" min="7" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="13">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="13" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>캐릭터 고유 ID</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>캐릭터 이름</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>캐릭터 설명</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>스킬 ID 목록</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>사용 무기 ID</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>기본 의상 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="13">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>SkillList</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>UseWeaponId</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>BasicCostumeId</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>character_narrator_01</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>나레이션</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>프롤로그와 에필로그를 진행하는 서술자</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>character_Moran_02</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>모란</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>이 게임의 주인공</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>character_JangYoungSim_03</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장영심 </t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>이 게임의 주인공의 아버지</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>character_Mr.Jaeik_04</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>재익군</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>주인공의 첫번째 동료</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>character_Chunyang_05</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>주인공의 두번째 동료이자 재익의 주인</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="E25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="E26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="E27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="E28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1900,8 +1947,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Character.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Character.xlsx
@@ -1,90 +1,165 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Character" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DNTable_Character" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+  <si>
+    <t>캐릭터 고유 ID</t>
+  </si>
+  <si>
+    <t>캐릭터 이름</t>
+  </si>
+  <si>
+    <t>캐릭터 설명</t>
+  </si>
+  <si>
+    <t>스킬 ID 목록</t>
+  </si>
+  <si>
+    <t>사용 무기 ID</t>
+  </si>
+  <si>
+    <t>기본 의상 ID</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>SkillList</t>
+  </si>
+  <si>
+    <t>UseWeaponId</t>
+  </si>
+  <si>
+    <t>BasicCostumeId</t>
+  </si>
+  <si>
+    <t>character_narrator_01</t>
+  </si>
+  <si>
+    <t>나레이션</t>
+  </si>
+  <si>
+    <t>프롤로그와 에필로그를 진행하는 서술자</t>
+  </si>
+  <si>
+    <t>character_Moran_02</t>
+  </si>
+  <si>
+    <t>모란</t>
+  </si>
+  <si>
+    <t>이 게임의 주인공</t>
+  </si>
+  <si>
+    <t>character_JangYoungSim_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">장영심 </t>
+  </si>
+  <si>
+    <t>이 게임의 주인공의 아버지</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_04</t>
+  </si>
+  <si>
+    <t>재익군</t>
+  </si>
+  <si>
+    <t>주인공의 첫번째 동료</t>
+  </si>
+  <si>
+    <t>춘양</t>
+  </si>
+  <si>
+    <t>주인공의 두번째 동료이자 재익의 주인</t>
+  </si>
+  <si>
+    <t>촌장</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage1 NPC Stage1 임무를 주고 다시 받는다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Chunyang_05</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_VillageChief_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="6">
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF008000"/>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -115,29 +190,23 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -183,121 +252,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -498,502 +499,438 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O1000"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="15" customWidth="1" style="3" min="1" max="1"/>
-    <col width="14" customWidth="1" style="3" min="2" max="2"/>
-    <col width="14" customWidth="1" style="3" min="3" max="3"/>
-    <col width="14" customWidth="1" style="3" min="4" max="4"/>
-    <col width="14" customWidth="1" style="3" min="5" max="5"/>
-    <col width="14" customWidth="1" style="3" min="6" max="6"/>
-    <col width="12.54296875" customWidth="1" style="3" min="7" max="16384"/>
+    <col min="1" max="1" width="15" style="2" customWidth="1"/>
+    <col min="2" max="6" width="14" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="12.54296875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>캐릭터 고유 ID</t>
-        </is>
-      </c>
-      <c r="B1" s="17" t="inlineStr">
-        <is>
-          <t>캐릭터 이름</t>
-        </is>
-      </c>
-      <c r="C1" s="17" t="inlineStr">
-        <is>
-          <t>캐릭터 설명</t>
-        </is>
-      </c>
-      <c r="D1" s="17" t="inlineStr">
-        <is>
-          <t>스킬 ID 목록</t>
-        </is>
-      </c>
-      <c r="E1" s="17" t="inlineStr">
-        <is>
-          <t>사용 무기 ID</t>
-        </is>
-      </c>
-      <c r="F1" s="18" t="inlineStr">
-        <is>
-          <t>기본 의상 ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="13">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>SkillList</t>
-        </is>
-      </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>UseWeaponId</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>BasicCostumeId</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>character_narrator_01</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>나레이션</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>프롤로그와 에필로그를 진행하는 서술자</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>character_Moran_02</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>이 게임의 주인공</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>character_JangYoungSim_03</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">장영심 </t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>이 게임의 주인공의 아버지</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_04</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>재익군</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>주인공의 첫번째 동료</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>character_Chunyang_05</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>주인공의 두번째 동료이자 재익의 주인</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="1" t="n"/>
-      <c r="C10" s="1" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="n"/>
-      <c r="C11" s="1" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="E25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="E26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="E27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="E28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="13" customHeight="1">
+      <c r="A2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1947,7 +1884,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Character.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Character.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -110,6 +110,166 @@
   </si>
   <si>
     <t>character_VillageChief_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_GreedyDuck_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐관오리</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage2 보스 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_LeeMongRyong_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>이몽령</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage2 히어로</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깜짝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등장해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분위기를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시키고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>퀘스트를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돕니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -117,7 +277,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -155,6 +315,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="10">
@@ -711,9 +878,15 @@
       <c r="O9" s="4"/>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -728,10 +901,18 @@
       <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="4"/>
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>

--- a/JsonConverter/ExcelFiles/OO_Character.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Character.xlsx
@@ -122,10 +122,6 @@
   </si>
   <si>
     <t xml:space="preserve">Stage2 보스 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_LeeMongRyong_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -270,6 +266,10 @@
       </rPr>
       <t>.</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_LeeMongRyong_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -902,16 +902,16 @@
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>

--- a/JsonConverter/ExcelFiles/OO_Character.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Character.xlsx
@@ -1,332 +1,79 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DNTable_Character" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Character" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
-  <si>
-    <t>캐릭터 고유 ID</t>
-  </si>
-  <si>
-    <t>캐릭터 이름</t>
-  </si>
-  <si>
-    <t>캐릭터 설명</t>
-  </si>
-  <si>
-    <t>스킬 ID 목록</t>
-  </si>
-  <si>
-    <t>사용 무기 ID</t>
-  </si>
-  <si>
-    <t>기본 의상 ID</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>SkillList</t>
-  </si>
-  <si>
-    <t>UseWeaponId</t>
-  </si>
-  <si>
-    <t>BasicCostumeId</t>
-  </si>
-  <si>
-    <t>character_narrator_01</t>
-  </si>
-  <si>
-    <t>나레이션</t>
-  </si>
-  <si>
-    <t>프롤로그와 에필로그를 진행하는 서술자</t>
-  </si>
-  <si>
-    <t>character_Moran_02</t>
-  </si>
-  <si>
-    <t>모란</t>
-  </si>
-  <si>
-    <t>이 게임의 주인공</t>
-  </si>
-  <si>
-    <t>character_JangYoungSim_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">장영심 </t>
-  </si>
-  <si>
-    <t>이 게임의 주인공의 아버지</t>
-  </si>
-  <si>
-    <t>character_Mr.Jaeik_04</t>
-  </si>
-  <si>
-    <t>재익군</t>
-  </si>
-  <si>
-    <t>주인공의 첫번째 동료</t>
-  </si>
-  <si>
-    <t>춘양</t>
-  </si>
-  <si>
-    <t>주인공의 두번째 동료이자 재익의 주인</t>
-  </si>
-  <si>
-    <t>촌장</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stage1 NPC Stage1 임무를 주고 다시 받는다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Chunyang_05</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_VillageChief_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_GreedyDuck_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>탐관오리</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Stage2 보스 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>이몽령</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stage2 히어로</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>깜짝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등장해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>분위기를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>반전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시키고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>퀘스트를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>돕니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_LeeMongRyong_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="9">
     <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
+    </font>
+    <font>
+      <name val="?? ??"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -357,7 +104,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,6 +121,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -419,53 +171,124 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -666,452 +489,551 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="6" width="14" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="12.54296875" style="2"/>
+    <col width="15" customWidth="1" style="2" min="1" max="1"/>
+    <col width="14" customWidth="1" style="2" min="2" max="6"/>
+    <col width="12.54296875" customWidth="1" style="2" min="7" max="7"/>
+    <col width="12.54296875" customWidth="1" style="2" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="13" customHeight="1">
-      <c r="A2" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>캐릭터 고유 ID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>캐릭터 이름</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>캐릭터 설명</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>스킬 ID 목록</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>사용 무기 ID</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>기본 의상 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="11">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>SkillList</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>UseWeaponId</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>BasicCostumeId</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>character_narrator_01</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>나레이션</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>프롤로그와 에필로그를 진행하는 서술자</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>character_Moran_02</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>모란</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>이 게임의 주인공</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>character_JangYoungSim_03</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장영심 </t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>이 게임의 주인공의 아버지</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>character_Mr.Jaeik_04</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>재익군</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>주인공의 첫번째 동료</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>character_Chunyang_05</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>주인공의 두번째 동료이자 재익의 주인</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>character_VillageChief_01</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>촌장</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Stage1 NPC Stage1 임무를 주고 다시 받는다.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>character_GreedyDuck_01</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>탐관오리</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage2 보스 </t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>character_LeeMongRyong_01</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>이몽령</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Stage2 히어로</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>깜짝 등장해 분위기를 반전 시키고 퀘스트를 돕니다.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>character_Sangun_01</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>산군</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Stage3에서 등장하는 숲의 맹수. 꿀떡으로 분노를 누그러뜨릴 수 있다.</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr"/>
+      <c r="E12" s="19" t="inlineStr"/>
+      <c r="F12" s="19" t="inlineStr"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="E25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="E26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="E27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="E28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2065,8 +1987,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Character.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Character.xlsx
@@ -1,79 +1,234 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Character" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DNTable_Character" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+  <si>
+    <t>캐릭터 고유 ID</t>
+  </si>
+  <si>
+    <t>캐릭터 이름</t>
+  </si>
+  <si>
+    <t>캐릭터 설명</t>
+  </si>
+  <si>
+    <t>스킬 ID 목록</t>
+  </si>
+  <si>
+    <t>사용 무기 ID</t>
+  </si>
+  <si>
+    <t>기본 의상 ID</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>SkillList</t>
+  </si>
+  <si>
+    <t>UseWeaponId</t>
+  </si>
+  <si>
+    <t>BasicCostumeId</t>
+  </si>
+  <si>
+    <t>character_narrator_01</t>
+  </si>
+  <si>
+    <t>나레이션</t>
+  </si>
+  <si>
+    <t>프롤로그와 에필로그를 진행하는 서술자</t>
+  </si>
+  <si>
+    <t>character_Moran_02</t>
+  </si>
+  <si>
+    <t>모란</t>
+  </si>
+  <si>
+    <t>이 게임의 주인공</t>
+  </si>
+  <si>
+    <t>character_JangYoungSim_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">장영심 </t>
+  </si>
+  <si>
+    <t>이 게임의 주인공의 아버지</t>
+  </si>
+  <si>
+    <t>character_Mr.Jaeik_04</t>
+  </si>
+  <si>
+    <t>재익군</t>
+  </si>
+  <si>
+    <t>주인공의 첫번째 동료</t>
+  </si>
+  <si>
+    <t>character_Chunyang_05</t>
+  </si>
+  <si>
+    <t>춘양</t>
+  </si>
+  <si>
+    <t>주인공의 두번째 동료이자 재익의 주인</t>
+  </si>
+  <si>
+    <t>character_VillageChief_01</t>
+  </si>
+  <si>
+    <t>촌장</t>
+  </si>
+  <si>
+    <t>Stage1 NPC Stage1 임무를 주고 다시 받는다.</t>
+  </si>
+  <si>
+    <t>character_GreedyDuck_01</t>
+  </si>
+  <si>
+    <t>탐관오리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage2 보스 </t>
+  </si>
+  <si>
+    <t>character_LeeMongRyong_01</t>
+  </si>
+  <si>
+    <t>이몽령</t>
+  </si>
+  <si>
+    <t>Stage2 히어로</t>
+  </si>
+  <si>
+    <t>깜짝 등장해 분위기를 반전 시키고 퀘스트를 돕니다.</t>
+  </si>
+  <si>
+    <t>산군</t>
+  </si>
+  <si>
+    <t>Stage3에서 등장하는 숲의 맹수. 꿀떡으로 분노를 누그러뜨릴 수 있다.</t>
+  </si>
+  <si>
+    <t>character_Sangun_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>토끼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>거북이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Final Stage Boss</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage4_1 NPC</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage4_2 빌런</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Turtle_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Rabbit_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>연산군자</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_YeonSanJa_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="7">
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Arial"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="돋움"/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="?? ??"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="11">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -104,7 +259,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -125,7 +280,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,124 +326,56 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -489,551 +576,476 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O1000"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="15" customWidth="1" style="2" min="1" max="1"/>
-    <col width="14" customWidth="1" style="2" min="2" max="6"/>
-    <col width="12.54296875" customWidth="1" style="2" min="7" max="7"/>
-    <col width="12.54296875" customWidth="1" style="2" min="8" max="16384"/>
+    <col min="1" max="1" width="15" style="2" customWidth="1"/>
+    <col min="2" max="6" width="14" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.54296875" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="12.54296875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>캐릭터 고유 ID</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>캐릭터 이름</t>
-        </is>
-      </c>
-      <c r="C1" s="13" t="inlineStr">
-        <is>
-          <t>캐릭터 설명</t>
-        </is>
-      </c>
-      <c r="D1" s="13" t="inlineStr">
-        <is>
-          <t>스킬 ID 목록</t>
-        </is>
-      </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>사용 무기 ID</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>기본 의상 ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="11">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>SkillList</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>UseWeaponId</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>BasicCostumeId</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>character_narrator_01</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>나레이션</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>프롤로그와 에필로그를 진행하는 서술자</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>character_Moran_02</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>모란</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>이 게임의 주인공</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>character_JangYoungSim_03</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">장영심 </t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>이 게임의 주인공의 아버지</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>character_Mr.Jaeik_04</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>재익군</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>주인공의 첫번째 동료</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>character_Chunyang_05</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>춘양</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>주인공의 두번째 동료이자 재익의 주인</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>character_VillageChief_01</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>촌장</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Stage1 NPC Stage1 임무를 주고 다시 받는다.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>character_GreedyDuck_01</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>탐관오리</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stage2 보스 </t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>character_LeeMongRyong_01</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>이몽령</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Stage2 히어로</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>깜짝 등장해 분위기를 반전 시키고 퀘스트를 돕니다.</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>character_Sangun_01</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>산군</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>Stage3에서 등장하는 숲의 맹수. 꿀떡으로 분노를 누그러뜨릴 수 있다.</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr"/>
-      <c r="E12" s="19" t="inlineStr"/>
-      <c r="F12" s="19" t="inlineStr"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="8" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="8" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="E25" s="4" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="9" t="n"/>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="E26" s="4" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="9" t="n"/>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="E27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="9" t="n"/>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="E28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="9" t="n"/>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="9" t="n"/>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="10" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="10" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="13" customHeight="1">
+      <c r="A2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A12" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1987,7 +1999,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Character.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Character.xlsx
@@ -1,234 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DNTable_Character" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Character" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
-  <si>
-    <t>캐릭터 고유 ID</t>
-  </si>
-  <si>
-    <t>캐릭터 이름</t>
-  </si>
-  <si>
-    <t>캐릭터 설명</t>
-  </si>
-  <si>
-    <t>스킬 ID 목록</t>
-  </si>
-  <si>
-    <t>사용 무기 ID</t>
-  </si>
-  <si>
-    <t>기본 의상 ID</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>SkillList</t>
-  </si>
-  <si>
-    <t>UseWeaponId</t>
-  </si>
-  <si>
-    <t>BasicCostumeId</t>
-  </si>
-  <si>
-    <t>character_narrator_01</t>
-  </si>
-  <si>
-    <t>나레이션</t>
-  </si>
-  <si>
-    <t>프롤로그와 에필로그를 진행하는 서술자</t>
-  </si>
-  <si>
-    <t>character_Moran_02</t>
-  </si>
-  <si>
-    <t>모란</t>
-  </si>
-  <si>
-    <t>이 게임의 주인공</t>
-  </si>
-  <si>
-    <t>character_JangYoungSim_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">장영심 </t>
-  </si>
-  <si>
-    <t>이 게임의 주인공의 아버지</t>
-  </si>
-  <si>
-    <t>character_Mr.Jaeik_04</t>
-  </si>
-  <si>
-    <t>재익군</t>
-  </si>
-  <si>
-    <t>주인공의 첫번째 동료</t>
-  </si>
-  <si>
-    <t>character_Chunyang_05</t>
-  </si>
-  <si>
-    <t>춘양</t>
-  </si>
-  <si>
-    <t>주인공의 두번째 동료이자 재익의 주인</t>
-  </si>
-  <si>
-    <t>character_VillageChief_01</t>
-  </si>
-  <si>
-    <t>촌장</t>
-  </si>
-  <si>
-    <t>Stage1 NPC Stage1 임무를 주고 다시 받는다.</t>
-  </si>
-  <si>
-    <t>character_GreedyDuck_01</t>
-  </si>
-  <si>
-    <t>탐관오리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stage2 보스 </t>
-  </si>
-  <si>
-    <t>character_LeeMongRyong_01</t>
-  </si>
-  <si>
-    <t>이몽령</t>
-  </si>
-  <si>
-    <t>Stage2 히어로</t>
-  </si>
-  <si>
-    <t>깜짝 등장해 분위기를 반전 시키고 퀘스트를 돕니다.</t>
-  </si>
-  <si>
-    <t>산군</t>
-  </si>
-  <si>
-    <t>Stage3에서 등장하는 숲의 맹수. 꿀떡으로 분노를 누그러뜨릴 수 있다.</t>
-  </si>
-  <si>
-    <t>character_Sangun_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>토끼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>거북이</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Final Stage Boss</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stage4_1 NPC</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stage4_2 빌런</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Turtle_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Rabbit_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>연산군자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_YeonSanJa_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="7">
     <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="11">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -259,7 +95,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -327,55 +163,117 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -576,476 +474,587 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="6" width="14" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.54296875" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="12.54296875" style="2"/>
+    <col width="15" customWidth="1" style="2" min="1" max="1"/>
+    <col width="14" customWidth="1" style="2" min="2" max="6"/>
+    <col width="12.54296875" customWidth="1" style="2" min="7" max="8"/>
+    <col width="12.54296875" customWidth="1" style="2" min="9" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="13" customHeight="1">
-      <c r="A2" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>캐릭터 고유 ID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>캐릭터 이름</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>캐릭터 설명</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>스킬 ID 목록</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>사용 무기 ID</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>기본 의상 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="11">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>SkillList</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>UseWeaponId</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>BasicCostumeId</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>character_narrator_01</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>나레이션</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>이야기의 막을 열고 닫는 서술자입니다. 프롤로그와 에필로그에서 모란의 여정이 왜 시작되었고 어디로 향하는지 차분하게 안내합니다.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>character_Moran_02</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>모란</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>모란은 푸드카리지를 이끌고 길을 떠나는 주인공입니다. 각 지역에서 재료를 모으고 요리를 완성하며, 굶주린 사람들과 동물들의 문제를 해결해 나갑니다.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>character_JangYoungSim_03</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장영심 </t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>장영심은 모란의 아버지이자 따뜻한 마음을 가진 인물입니다. 귀한 쌀을 내어 주며 첫 여정의 계기를 만들고, 모란이 요리로 사람들을 돕게 하는 출발점이 됩니다.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>character_Mr.Jaeik_04</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>재익군</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>재익군은 모란과 함께 길을 나서는 든든한 동료입니다. 위험한 상황에서도 곁을 지키며, 산군과의 조우 이후에는 모란과 함께 승리의 기쁨을 나눕니다.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>character_Chunyang_05</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>춘양은 초반 여정에서 모란을 돕는 화자이자 동료입니다. 부드럽고 따뜻한 말투로 상황을 설명하며, 플레이어가 첫 임무와 세계관을 자연스럽게 이해하도록 도와줍니다.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>character_VillageChief_01</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>촌장</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>촌장은 동쪽 마을의 사정을 전하는 인물입니다. 굶주린 백성들을 위해 음식을 부탁하고, 모란이 만든 요리를 통해 첫 스테이지 임무를 완성하게 합니다.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>character_GreedyDuck_01</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>탐관오리</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>탐관오리는 서쪽 도시를 어지럽히는 탐욕스러운 권력자입니다. 백성들의 고통보다 자신의 배를 채우는 데 몰두하며, Stage2의 갈등을 만들어 내는 핵심 인물입니다.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>character_LeeMongRyong_01</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>이몽령</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>이몽령은 Stage2에서 등장하는 조력자입니다. 어두운 저택의 분위기를 뒤집고, 모란이 탐관오리의 탐욕을 넘어서 다음 여정으로 나아가게 돕습니다.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>깜짝 등장해 분위기를 반전 시키고 퀘스트를 돕니다.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>character_Sangun_01</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>산군</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>산군은 깊은 숲에서 만나는 강력한 존재입니다. 처음에는 위협적으로 등장하지만, 떡과 꿀로 만든 꿀떡을 통해 분노를 누그러뜨릴 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>character_Turtle_01</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>거북이</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>거북이는 Stage4_1에서 마지막 의뢰를 건네는 인물입니다. 토끼에게 당한 일을 모란에게 부탁하고, 토끼를 잠재운 뒤 돌아오면 최종 임무 완료로 이어 줍니다.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>character_Rabbit_01</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>토끼</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>토끼는 Stage4_2에서 멀리서 놀리듯 등장하는 장난기 많은 캐릭터입니다. 당근전을 좋아하며, 모란은 요리를 이용해 토끼를 유혹하고 잠들게 해야 합니다.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>character_YeonSanJa_01</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>연산군자</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>연산군자는 최종 장면에서 마주하는 인물입니다. 모란의 여정과 요리가 마지막으로 닿는 대상으로, 엔딩 직전의 긴장과 해소를 담당합니다.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="E25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="E26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="E27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="E28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1999,8 +2008,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>